--- a/output/graficos_dimensiones/comunal_e_matricula_a_2020_magallanes.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2020_magallanes.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:23</t>
+    <t xml:space="preserve">2026-09-10 01:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2020_magallanes.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2020_magallanes.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comunas'!$A$1:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comunas'!$A$1:$I$11</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t xml:space="preserve">Comuna</t>
   </si>
@@ -75,9 +75,6 @@
     <t xml:space="preserve">Natales</t>
   </si>
   <si>
-    <t xml:space="preserve">Torres del Paine</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -87,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:38</t>
+    <t xml:space="preserve">2026-09-18 11:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -476,7 +473,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="18.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="27.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="23.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="22.71" hidden="0" customWidth="1"/>
@@ -758,21 +755,8 @@
         <v>47.2</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I12"/>
+  <autoFilter ref="A1:I11"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -789,58 +773,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2020_magallanes.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2020_magallanes.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comunas'!$A$1:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comunas'!$A$1:$I$12</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t xml:space="preserve">Comuna</t>
   </si>
@@ -75,6 +75,9 @@
     <t xml:space="preserve">Natales</t>
   </si>
   <si>
+    <t xml:space="preserve">Torres del Paine</t>
+  </si>
+  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -84,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:34</t>
+    <t xml:space="preserve">2026-09-23 15:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -473,7 +476,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="18.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="27.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="23.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="22.71" hidden="0" customWidth="1"/>
@@ -755,8 +758,21 @@
         <v>47.2</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I11"/>
+  <autoFilter ref="A1:I12"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -773,58 +789,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2020_magallanes.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2020_magallanes.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:39</t>
+    <t xml:space="preserve">2026-10-05 16:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
